--- a/output/pdf_financials_xlsx/FBF.xlsx
+++ b/output/pdf_financials_xlsx/FBF.xlsx
@@ -967,16 +967,16 @@
         <v>0.426838</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.413827</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>0.709183</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>0.806942</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>0.961969</v>
       </c>
     </row>
     <row r="11">
@@ -1028,16 +1028,16 @@
         <v>0.460996</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>1.070338</v>
+        <v>0.656511</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>2.344566</v>
+        <v>1.635383</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>1.694408</v>
+        <v>0.887466</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>1.595257</v>
+        <v>0.633288</v>
       </c>
     </row>
     <row r="12">
@@ -2485,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.025095</v>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
@@ -2493,22 +2493,22 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.061781</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.090598</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.176852</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.352312</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.500968</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.878154</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0.831894</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.025095</v>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
@@ -2607,22 +2607,22 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.061781</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.090598</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.176852</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.352312</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.500968</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.878154</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>2.850528</v>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.006148</v>
+        <v>0</v>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
@@ -7985,16 +7985,16 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.06122</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.122437</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.122437</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.122437</v>
       </c>
     </row>
     <row r="125">
@@ -8052,16 +8052,16 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.06122</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.122437</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.122437</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.122437</v>
       </c>
     </row>
     <row r="126">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23370,7 +23370,11 @@
           <t>Lease payments 18</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -34388,7 +34392,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -34452,16 +34456,16 @@
         </is>
       </c>
       <c r="Q272" s="5" t="n">
-        <v>-0.413827</v>
+        <v>0.413827</v>
       </c>
       <c r="R272" s="5" t="n">
-        <v>-0.709183</v>
+        <v>0.709183</v>
       </c>
       <c r="S272" s="5" t="n">
-        <v>-0.806942</v>
+        <v>0.806942</v>
       </c>
       <c r="T272" s="5" t="n">
-        <v>-0.961969</v>
+        <v>0.961969</v>
       </c>
     </row>
     <row r="273">
@@ -40366,7 +40370,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">

--- a/output/pdf_financials_xlsx/FBF.xlsx
+++ b/output/pdf_financials_xlsx/FBF.xlsx
@@ -2173,22 +2173,22 @@
         <v>0.017332</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.015086</v>
+        <v>0.013328</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.115016</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.057012</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.114024</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.114024</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.114024</v>
       </c>
     </row>
     <row r="29">
@@ -2240,22 +2240,22 @@
         <v>0.284248</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.405909</v>
+        <v>0.404151</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.450715</v>
+        <v>0.565731</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.6614679999999999</v>
+        <v>0.71848</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.723111</v>
+        <v>1.837135</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.06776</v>
+        <v>1.181784</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.787986</v>
+        <v>0.90201</v>
       </c>
     </row>
     <row r="30">
@@ -2307,22 +2307,22 @@
         <v>11.79431727745824</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>14.3938136696709</v>
+        <v>14.33147377469128</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>15.58644691672162</v>
+        <v>19.56388449606479</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>25.52880765245179</v>
+        <v>27.72913840447847</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>28.09955832883791</v>
+        <v>29.95899979191685</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>22.80585293838729</v>
+        <v>25.24124532567158</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>16.64833134486469</v>
+        <v>19.05739614203983</v>
       </c>
     </row>
     <row r="31">
@@ -6399,22 +6399,22 @@
         <v>0.017332</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0.015086</v>
+        <v>0.013328</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.115016</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.057012</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.114024</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.114024</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.114024</v>
       </c>
     </row>
     <row r="101">
@@ -21786,7 +21786,11 @@
           <t>Depreciation - right-of-use assets 14</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -25442,7 +25446,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -25536,7 +25544,11 @@
           <t>Depreciation of right of use asset 9</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
